--- a/output/pdf_financials_xlsx/SHL.xlsx
+++ b/output/pdf_financials_xlsx/SHL.xlsx
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00704</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001685</v>
       </c>
     </row>
     <row r="13">
@@ -1397,13 +1397,13 @@
         <v>-10.659386</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.814181</v>
+        <v>-5.821221</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.320408</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.968495</v>
+        <v>-4.97018</v>
       </c>
     </row>
     <row r="28">
@@ -1465,13 +1465,13 @@
         <v>-10.659386</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.814181</v>
+        <v>-5.821221</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.320408</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.968495</v>
+        <v>-4.97018</v>
       </c>
     </row>
     <row r="30">
@@ -1626,31 +1626,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000186</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.044218</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001256</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.024157</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.713701</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.213772</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.172269</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.307356</v>
       </c>
     </row>
     <row r="35">
@@ -1694,31 +1694,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.025555</v>
+        <v>0.025741</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.016736</v>
+        <v>0.060954</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.000154</v>
+        <v>0.00141</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.000154</v>
+        <v>0.024311</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.713701</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.213772</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.172269</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.307356</v>
       </c>
     </row>
     <row r="37">
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.024121</v>
+        <v>0.023935</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.054867</v>
+        <v>0.010649</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.026344</v>
+        <v>0.025088</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.108837</v>
+        <v>0.08468000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>4.758892</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>8.133946</v>
+        <v>7.420245</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>9.317890999999999</v>
+        <v>9.104119000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>7.490299</v>
+        <v>7.31803</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.917653</v>
+        <v>3.610297</v>
       </c>
     </row>
     <row r="49">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -19436,7 +19436,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">

--- a/output/pdf_financials_xlsx/SHL.xlsx
+++ b/output/pdf_financials_xlsx/SHL.xlsx
@@ -952,7 +952,7 @@
         <v>8.613864</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-10.659386</v>
+        <v>-12.291467</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-5.814181</v>
@@ -980,13 +980,13 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.002745</v>
+        <v>-0.002745</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>1.632081</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1394,7 +1394,7 @@
         <v>8.613864</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-10.659386</v>
+        <v>-12.291467</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5.821221</v>
@@ -1462,7 +1462,7 @@
         <v>8.613864</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-10.659386</v>
+        <v>-12.291467</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.821221</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-13.27816281002097</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -2682,10 +2682,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.02853</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.064787</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -2784,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.063511</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.151236</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -3921,13 +3921,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0.001526</v>
+        <v>-0.040112</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.001016</v>
+        <v>0.035154</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.006767</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.07656200000000001</v>
@@ -4091,13 +4091,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.244755</v>
+        <v>0.203117</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.226145</v>
+        <v>-0.192007</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.159279</v>
+        <v>0.166046</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.030416</v>
@@ -4242,10 +4242,10 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.018981</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.013679</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.009379999999999999</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
@@ -4412,16 +4412,16 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.263064</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>1.620451</v>
       </c>
     </row>
     <row r="116">
@@ -10655,7 +10655,11 @@
           <t>Net proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -11015,7 +11019,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -11497,7 +11505,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -12713,7 +12725,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -13232,7 +13248,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -13708,7 +13728,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -14182,7 +14206,11 @@
           <t>Cash from private placement</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E153" s="5" t="n">
         <v>0.2</v>
       </c>
@@ -14465,7 +14493,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -14760,7 +14792,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
         <v>-0.041638</v>
       </c>
@@ -20526,7 +20562,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -23195,7 +23235,11 @@
           <t>Income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
